--- a/artfynd/A 54112-2022 artfynd.xlsx
+++ b/artfynd/A 54112-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54112-2022 artfynd.xlsx
+++ b/artfynd/A 54112-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93293497</v>
+        <v>93293501</v>
       </c>
       <c r="B2" t="n">
-        <v>57068</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103057</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509499.6890728427</v>
+        <v>509500</v>
       </c>
       <c r="R2" t="n">
-        <v>6551093.555819199</v>
+        <v>6551094</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,24 +755,9 @@
           <t>2021-05-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kärret V om</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93293539</v>
+        <v>93293497</v>
       </c>
       <c r="B3" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>103057</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -842,29 +817,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sannahed, grusgrop NO, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509499.6890728427</v>
+        <v>509500</v>
       </c>
       <c r="R3" t="n">
-        <v>6551093.555819199</v>
+        <v>6551094</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -894,19 +864,14 @@
           <t>2021-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kärret V om</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -934,37 +898,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93293501</v>
+        <v>93293539</v>
       </c>
       <c r="B4" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>208255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -972,24 +931,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sannahed, grusgrop NO, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509499.6890728427</v>
+        <v>509500</v>
       </c>
       <c r="R4" t="n">
-        <v>6551093.555819199</v>
+        <v>6551094</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1019,19 +983,9 @@
           <t>2021-05-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +994,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54112-2022 artfynd.xlsx
+++ b/artfynd/A 54112-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93293501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93293497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135010703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93293539</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54112-2022 artfynd.xlsx
+++ b/artfynd/A 54112-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135010703</v>
       </c>
       <c r="B4" t="n">
-        <v>45048</v>
+        <v>45053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
